--- a/jogos_2025-01-01.xlsx
+++ b/jogos_2025-01-01.xlsx
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.26</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.76</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['5', '37', '56']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['50', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['32', '56']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45658.39583333334</v>
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
         <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AA6" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['5', '37', '56']</t>
+          <t>['50', '90+1']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['32', '56']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45658.39583333334</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
         <v>2.5</v>
@@ -1605,16 +1605,16 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AA9" t="n">
         <v>2.49</v>
@@ -1623,14 +1623,14 @@
         <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['53', '87']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.53</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>4.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45658.47916666666</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
         <v>2.5</v>
@@ -1734,16 +1734,16 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AA10" t="n">
         <v>2.49</v>
@@ -1752,14 +1752,14 @@
         <v>1.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['53', '87']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.3</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45658.47916666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.5</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['39', '56']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.5</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['6', '26']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['42', '77']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45658.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['11', '24']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45658.5</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
         <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['72', '84']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45658.5</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2370,59 +2370,59 @@
         <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
         <v>3.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AA15" t="n">
         <v>3.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['44', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['22', '29', '61', '78']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45658.5</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,55 +2475,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
         <v>1.91</v>
@@ -2538,20 +2538,20 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['39', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45658.5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['32', '74']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['9', '39', '53']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.57</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['50', '64']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45658.5</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.38</v>
       </c>
-      <c r="P18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['6', '26']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['42', '77']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI18" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['18', '35', '40']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45658.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['15', '82', '90+8']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['44', '61']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.5</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45658.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2994,58 +2994,58 @@
         <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y20" t="n">
         <v>3</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="Z20" t="n">
         <v>1.36</v>
       </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3054,20 +3054,20 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45658.5</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>3.4</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['20', '36']</t>
+          <t>['32', '90+3', '90+8']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['21', '78']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45658.5</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['20', '36']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45658.5</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,16 +3352,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>2</v>
@@ -3370,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y23" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.89</v>
-      </c>
       <c r="Z23" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['8', '61', '63', '74']</t>
+          <t>['45+2', '78']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['68', '90+1']</t>
+          <t>['23', '86']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45658.5</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['11', '24']</t>
+          <t>['22', '29', '61', '78']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45658.5</v>
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
         <v>1.95</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q25" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="X25" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45658.5</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,16 +3739,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -3757,7 +3757,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O26" t="n">
         <v>2.6</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['8', '61', '63', '74']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['68', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>2.6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['45+2', '78']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['23', '86']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45658.5</v>
@@ -3868,16 +3868,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O27" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
         <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['66', '90+4']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45658.5</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['9', '60', '82']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['5', '39']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['72', '84']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45658.5</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.4</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
         <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['65', '82']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45658.5</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
         <v>3.6</v>
       </c>
       <c r="N30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>4.33</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.75</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X30" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['44', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45658.5</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="n">
         <v>2.5</v>
       </c>
-      <c r="M31" t="n">
+      <c r="T31" t="n">
         <v>3.5</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="U31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="AD31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['18', '35', '40']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>3.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['9', '60', '82']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['5', '39']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45658.5</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="P32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3.5</v>
       </c>
-      <c r="N32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.75</v>
       </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2</v>
-      </c>
       <c r="AD32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['32', '90+3', '90+8']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['21', '78']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45658.5</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4789,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4800,80 +4800,80 @@
         <v>1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="O34" t="n">
         <v>2.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.4</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X34" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['66', '90+4']</t>
+          <t>['50', '64']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AI34" t="n">
         <v>1.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45658.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,22 +4926,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
         <v>1.53</v>
@@ -4950,10 +4950,10 @@
         <v>2.38</v>
       </c>
       <c r="T35" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V35" t="n">
         <v>1.08</v>
@@ -4965,10 +4965,10 @@
         <v>2.7</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AA35" t="n">
         <v>4.75</v>
@@ -4977,10 +4977,10 @@
         <v>1.18</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45658.5</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P36" t="n">
         <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R36" t="n">
         <v>1.4</v>
@@ -5079,19 +5079,19 @@
         <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
         <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y36" t="n">
         <v>1.92</v>
@@ -5100,38 +5100,38 @@
         <v>1.82</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.19</v>
+        <v>1.66</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45658.5</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>3</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="T37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA37" t="n">
         <v>3.3</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="AB37" t="n">
         <v>1.33</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC37" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['32', '74']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['9', '39', '53']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45658.5</v>
@@ -5287,16 +5287,16 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
@@ -5305,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
         <v>1.4</v>
@@ -5337,13 +5337,13 @@
         <v>2.75</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
         <v>1.3</v>
@@ -5352,10 +5352,10 @@
         <v>3.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AA38" t="n">
         <v>3.4</v>
@@ -5371,25 +5371,25 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['15', '82', '90+8']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['44', '61']</t>
+          <t>['65', '82']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45658.5</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5431,10 +5431,10 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,34 +5442,34 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
         <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
         <v>1.05</v>
@@ -5478,47 +5478,47 @@
         <v>1.3</v>
       </c>
       <c r="X39" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45658.5</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5961,80 +5961,80 @@
         <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P43" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="S43" t="n">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="T43" t="n">
-        <v>2.39</v>
+        <v>3.46</v>
       </c>
       <c r="U43" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="X43" t="n">
-        <v>4.3</v>
+        <v>2.46</v>
       </c>
       <c r="Y43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['33', '58', '81']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45658.625</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>1</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6090,80 +6090,80 @@
         <v>3.3</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P44" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="R44" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="T44" t="n">
-        <v>3.46</v>
+        <v>2.39</v>
       </c>
       <c r="U44" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="V44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="X44" t="n">
-        <v>2.46</v>
+        <v>4.3</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z44" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z44" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA44" t="n">
-        <v>4.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AD44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['33', '58', '81']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45658.625</v>
